--- a/SGC-CKN/Excel/536d3011-c5c3-4569-b53f-e94340580854_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P1-6_D800_20-03-2026.xlsx
+++ b/SGC-CKN/Excel/536d3011-c5c3-4569-b53f-e94340580854_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P1-6_D800_20-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="67">
   <si>
     <t>Dự án</t>
   </si>
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>P1-6</t>
+    <t>P7-06</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>
@@ -115,7 +115,7 @@
     <t>Cát pha xám ghi, xám nâu TT dẻo</t>
   </si>
   <si>
-    <t xml:space="preserve">09:30
+    <t xml:space="preserve">09:50
 20/03/2026</t>
   </si>
   <si>
@@ -133,10 +133,6 @@
   </si>
   <si>
     <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11:20
-20/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">12:00
@@ -1245,13 +1241,13 @@
         <v>-8.5</v>
       </c>
       <c r="H12" s="9">
-        <v>0.83</v>
+        <v>1.17</v>
       </c>
       <c r="I12" s="9">
         <v>2</v>
       </c>
       <c r="J12" s="12">
-        <v>2.4</v>
+        <v>1.71</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>30</v>
@@ -1280,13 +1276,13 @@
         <v>-16.7</v>
       </c>
       <c r="H13" s="13">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="I13" s="13">
         <v>8.2</v>
       </c>
       <c r="J13" s="8">
-        <v>5.47</v>
+        <v>7.03</v>
       </c>
       <c r="K13" s="14" t="s">
         <v>30</v>
@@ -1303,10 +1299,10 @@
         <v>38</v>
       </c>
       <c r="D14" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="E14" s="18" t="s">
         <v>39</v>
-      </c>
-      <c r="E14" s="18" t="s">
-        <v>40</v>
       </c>
       <c r="F14" s="16">
         <v>-16.7</v>
@@ -1315,13 +1311,13 @@
         <v>-21</v>
       </c>
       <c r="H14" s="16">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="I14" s="16">
         <v>4.3</v>
       </c>
-      <c r="J14" s="8">
-        <v>6.45</v>
+      <c r="J14" s="12">
+        <v>4.3</v>
       </c>
       <c r="K14" s="17" t="s">
         <v>30</v>
@@ -1329,19 +1325,19 @@
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="20" t="s">
+      <c r="D15" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="E15" s="21" t="s">
         <v>42</v>
-      </c>
-      <c r="D15" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="E15" s="21" t="s">
-        <v>43</v>
       </c>
       <c r="F15" s="19">
         <v>-21</v>
@@ -1364,34 +1360,34 @@
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="B16" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="23" t="s">
+      <c r="D16" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="E16" s="24" t="s">
         <v>45</v>
-      </c>
-      <c r="D16" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="E16" s="24" t="s">
-        <v>46</v>
       </c>
       <c r="F16" s="22">
         <v>-25.01</v>
       </c>
       <c r="G16" s="22">
-        <v>-34.95</v>
+        <v>-34.05</v>
       </c>
       <c r="H16" s="22">
         <v>0.33</v>
       </c>
       <c r="I16" s="22">
-        <v>9.94</v>
+        <v>9.04</v>
       </c>
       <c r="J16" s="8">
-        <v>29.82</v>
+        <v>27.12</v>
       </c>
       <c r="K16" s="23" t="s">
         <v>30</v>
@@ -1399,22 +1395,22 @@
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="B17" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="26" t="s">
+      <c r="D17" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="E17" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="D17" s="27" t="s">
-        <v>46</v>
-      </c>
-      <c r="E17" s="27" t="s">
-        <v>49</v>
-      </c>
       <c r="F17" s="25">
-        <v>-34.95</v>
+        <v>-34.05</v>
       </c>
       <c r="G17" s="25">
         <v>-37.5</v>
@@ -1423,10 +1419,10 @@
         <v>0.33</v>
       </c>
       <c r="I17" s="25">
-        <v>2.55</v>
+        <v>3.45</v>
       </c>
       <c r="J17" s="8">
-        <v>7.65</v>
+        <v>10.35</v>
       </c>
       <c r="K17" s="26" t="s">
         <v>30</v>
@@ -1434,19 +1430,19 @@
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="B18" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="29" t="s">
+      <c r="D18" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="E18" s="30" t="s">
         <v>51</v>
-      </c>
-      <c r="D18" s="30" t="s">
-        <v>49</v>
-      </c>
-      <c r="E18" s="30" t="s">
-        <v>52</v>
       </c>
       <c r="F18" s="28">
         <v>-37.5</v>
@@ -1469,19 +1465,19 @@
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="31" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B19" s="31" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="32" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="E19" s="33" t="s">
         <v>53</v>
-      </c>
-      <c r="D19" s="33" t="s">
-        <v>52</v>
-      </c>
-      <c r="E19" s="33" t="s">
-        <v>54</v>
       </c>
       <c r="F19" s="31">
         <v>-39.5</v>
@@ -1504,19 +1500,19 @@
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="B20" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="35" t="s">
         <v>55</v>
       </c>
-      <c r="B20" s="34" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="35" t="s">
+      <c r="D20" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="E20" s="36" t="s">
         <v>56</v>
-      </c>
-      <c r="D20" s="36" t="s">
-        <v>54</v>
-      </c>
-      <c r="E20" s="36" t="s">
-        <v>57</v>
       </c>
       <c r="F20" s="34">
         <v>-43.16</v>
@@ -1539,7 +1535,7 @@
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="37" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B23" s="37"/>
       <c r="C23" s="37"/>
@@ -1645,31 +1641,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1721,13 +1717,13 @@
         <v>-8.5</v>
       </c>
       <c r="G3" s="9">
-        <v>0.83</v>
+        <v>1.17</v>
       </c>
       <c r="H3" s="9">
         <v>2</v>
       </c>
       <c r="I3" s="12">
-        <v>2.4</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1750,13 +1746,13 @@
         <v>-16.7</v>
       </c>
       <c r="G4" s="13">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="H4" s="13">
         <v>8.2</v>
       </c>
       <c r="I4" s="8">
-        <v>5.47</v>
+        <v>7.03</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1779,13 +1775,13 @@
         <v>-21</v>
       </c>
       <c r="G5" s="16">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="H5" s="16">
         <v>4.3</v>
       </c>
-      <c r="I5" s="8">
-        <v>6.45</v>
+      <c r="I5" s="12">
+        <v>4.3</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1796,7 +1792,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D6" s="19">
         <v>1</v>
@@ -1825,7 +1821,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D7" s="22">
         <v>1</v>
@@ -1834,16 +1830,16 @@
         <v>-25.01</v>
       </c>
       <c r="F7" s="22">
-        <v>-34.95</v>
+        <v>-34.05</v>
       </c>
       <c r="G7" s="22">
         <v>0.33</v>
       </c>
       <c r="H7" s="22">
-        <v>9.94</v>
+        <v>9.04</v>
       </c>
       <c r="I7" s="8">
-        <v>29.82</v>
+        <v>27.12</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1854,13 +1850,13 @@
         <v>11</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D8" s="25">
         <v>1</v>
       </c>
       <c r="E8" s="25">
-        <v>-34.95</v>
+        <v>-34.05</v>
       </c>
       <c r="F8" s="25">
         <v>-37.5</v>
@@ -1869,10 +1865,10 @@
         <v>0.33</v>
       </c>
       <c r="H8" s="25">
-        <v>2.55</v>
+        <v>3.45</v>
       </c>
       <c r="I8" s="8">
-        <v>7.65</v>
+        <v>10.35</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1883,7 +1879,7 @@
         <v>11</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D9" s="28">
         <v>1</v>
@@ -1912,7 +1908,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D10" s="31">
         <v>1</v>
@@ -1941,7 +1937,7 @@
         <v>11</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D11" s="34">
         <v>1</v>
@@ -1964,7 +1960,7 @@
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="38" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B12" s="39" t="s">
         <v>30</v>
@@ -1982,13 +1978,13 @@
         <v>-44.75</v>
       </c>
       <c r="G12" s="39">
-        <v>5.67</v>
+        <v>6</v>
       </c>
       <c r="H12" s="39">
         <v>44.75</v>
       </c>
       <c r="I12" s="39">
-        <v>7.9</v>
+        <v>7.46</v>
       </c>
     </row>
   </sheetData>

--- a/SGC-CKN/Excel/536d3011-c5c3-4569-b53f-e94340580854_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P1-6_D800_20-03-2026.xlsx
+++ b/SGC-CKN/Excel/536d3011-c5c3-4569-b53f-e94340580854_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P1-6_D800_20-03-2026.xlsx
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>P7-06</t>
+    <t>P1-6</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>
@@ -1378,16 +1378,16 @@
         <v>-25.01</v>
       </c>
       <c r="G16" s="22">
-        <v>-34.05</v>
+        <v>-34.95</v>
       </c>
       <c r="H16" s="22">
         <v>0.33</v>
       </c>
       <c r="I16" s="22">
-        <v>9.04</v>
+        <v>9.94</v>
       </c>
       <c r="J16" s="8">
-        <v>27.12</v>
+        <v>29.82</v>
       </c>
       <c r="K16" s="23" t="s">
         <v>30</v>
@@ -1410,7 +1410,7 @@
         <v>48</v>
       </c>
       <c r="F17" s="25">
-        <v>-34.05</v>
+        <v>-34.95</v>
       </c>
       <c r="G17" s="25">
         <v>-37.5</v>
@@ -1419,10 +1419,10 @@
         <v>0.33</v>
       </c>
       <c r="I17" s="25">
-        <v>3.45</v>
+        <v>2.55</v>
       </c>
       <c r="J17" s="8">
-        <v>10.35</v>
+        <v>7.65</v>
       </c>
       <c r="K17" s="26" t="s">
         <v>30</v>
@@ -1830,16 +1830,16 @@
         <v>-25.01</v>
       </c>
       <c r="F7" s="22">
-        <v>-34.05</v>
+        <v>-34.95</v>
       </c>
       <c r="G7" s="22">
         <v>0.33</v>
       </c>
       <c r="H7" s="22">
-        <v>9.04</v>
+        <v>9.94</v>
       </c>
       <c r="I7" s="8">
-        <v>27.12</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1856,7 +1856,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="25">
-        <v>-34.05</v>
+        <v>-34.95</v>
       </c>
       <c r="F8" s="25">
         <v>-37.5</v>
@@ -1865,10 +1865,10 @@
         <v>0.33</v>
       </c>
       <c r="H8" s="25">
-        <v>3.45</v>
+        <v>2.55</v>
       </c>
       <c r="I8" s="8">
-        <v>10.35</v>
+        <v>7.65</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">

--- a/SGC-CKN/Excel/536d3011-c5c3-4569-b53f-e94340580854_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P1-6_D800_20-03-2026.xlsx
+++ b/SGC-CKN/Excel/536d3011-c5c3-4569-b53f-e94340580854_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P1-6_D800_20-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="66">
   <si>
     <t>Dự án</t>
   </si>
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>P1-6</t>
+    <t>P7-06</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>
@@ -92,10 +92,10 @@
     <t>Ghi chú</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen, xám trắng, xám xanh TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">08:00
@@ -109,10 +109,10 @@
     <t/>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>Cát pha xám ghi, xám nâu TT dẻo</t>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Cát pha xám ghi, xám nâu, xám vàng TT dẻo</t>
   </si>
   <si>
     <t xml:space="preserve">09:50
@@ -129,40 +129,40 @@
 20/03/2026</t>
   </si>
   <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Sét xám vàng, nâu vàng, xám xanh, TT nửa cứng</t>
   </si>
   <si>
     <t xml:space="preserve">12:00
 20/03/2026</t>
   </si>
   <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Cát thô vừa, xám vàng, xám xanh, TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
     <t xml:space="preserve">12:30
 20/03/2026</t>
   </si>
   <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
+    <t>6</t>
+  </si>
+  <si>
+    <t>Cát thô, xám vàng, xám xanh, xám nâu, KC chặt</t>
   </si>
   <si>
     <t xml:space="preserve">12:50
 20/03/2026</t>
   </si>
   <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
+    <t>7</t>
+  </si>
+  <si>
+    <t>Sỏi xám vàng, nâu vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">13:10
@@ -172,24 +172,21 @@
     <t>8</t>
   </si>
   <si>
-    <t>TK-16.1.Cát xám, xám vàng, xám xanh, TT rất chặt</t>
+    <t>Cát xám, xám vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">13:30
 20/03/2026</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
-  </si>
-  <si>
     <t xml:space="preserve">13:50
 20/03/2026</t>
   </si>
   <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>Cuội đa màu sắc TT rất chặt</t>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Cuội đa màu sắc, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">14:00
@@ -1378,16 +1375,16 @@
         <v>-25.01</v>
       </c>
       <c r="G16" s="22">
-        <v>-34.95</v>
+        <v>-34.05</v>
       </c>
       <c r="H16" s="22">
         <v>0.33</v>
       </c>
       <c r="I16" s="22">
-        <v>9.94</v>
+        <v>9.04</v>
       </c>
       <c r="J16" s="8">
-        <v>29.82</v>
+        <v>27.12</v>
       </c>
       <c r="K16" s="23" t="s">
         <v>30</v>
@@ -1410,7 +1407,7 @@
         <v>48</v>
       </c>
       <c r="F17" s="25">
-        <v>-34.95</v>
+        <v>-34.05</v>
       </c>
       <c r="G17" s="25">
         <v>-37.5</v>
@@ -1419,10 +1416,10 @@
         <v>0.33</v>
       </c>
       <c r="I17" s="25">
-        <v>2.55</v>
+        <v>3.45</v>
       </c>
       <c r="J17" s="8">
-        <v>7.65</v>
+        <v>10.35</v>
       </c>
       <c r="K17" s="26" t="s">
         <v>30</v>
@@ -1465,19 +1462,19 @@
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="31" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="B19" s="31" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="32" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D19" s="33" t="s">
         <v>51</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F19" s="31">
         <v>-39.5</v>
@@ -1500,19 +1497,19 @@
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="34" t="s">
+        <v>53</v>
+      </c>
+      <c r="B20" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="B20" s="34" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="35" t="s">
+      <c r="D20" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="E20" s="36" t="s">
         <v>55</v>
-      </c>
-      <c r="D20" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="E20" s="36" t="s">
-        <v>56</v>
       </c>
       <c r="F20" s="34">
         <v>-43.16</v>
@@ -1535,7 +1532,7 @@
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="37" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B23" s="37"/>
       <c r="C23" s="37"/>
@@ -1641,31 +1638,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1830,16 +1827,16 @@
         <v>-25.01</v>
       </c>
       <c r="F7" s="22">
-        <v>-34.95</v>
+        <v>-34.05</v>
       </c>
       <c r="G7" s="22">
         <v>0.33</v>
       </c>
       <c r="H7" s="22">
-        <v>9.94</v>
+        <v>9.04</v>
       </c>
       <c r="I7" s="8">
-        <v>29.82</v>
+        <v>27.12</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1856,7 +1853,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="25">
-        <v>-34.95</v>
+        <v>-34.05</v>
       </c>
       <c r="F8" s="25">
         <v>-37.5</v>
@@ -1865,10 +1862,10 @@
         <v>0.33</v>
       </c>
       <c r="H8" s="25">
-        <v>2.55</v>
+        <v>3.45</v>
       </c>
       <c r="I8" s="8">
-        <v>7.65</v>
+        <v>10.35</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1908,7 +1905,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D10" s="31">
         <v>1</v>
@@ -1937,7 +1934,7 @@
         <v>11</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D11" s="34">
         <v>1</v>
@@ -1960,7 +1957,7 @@
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="38" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B12" s="39" t="s">
         <v>30</v>
